--- a/agent_runs/manjidiwang/episodes/ep23/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep23/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>碎瓶逼问 （，总时长：10秒，镜头数：5个）</t>
+          <t>碎瓶逼问</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>毒丸烟雾 （，总时长：10秒，镜头数：4个）</t>
+          <t>毒丸烟雾</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>旧约触发 （，总时长：10秒，镜头数：2个）</t>
+          <t>旧约触发</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>十步棋局 （，总时长：11秒，镜头数：4个）</t>
+          <t>十步棋局</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>窗边卖身契 （，总时长：10秒，镜头数：3个）</t>
+          <t>窗边卖身契</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>通报落桌 （，总时长：11秒，镜头数：4个）</t>
+          <t>通报落桌</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>接管前夜 （，总时长：10秒，镜头数：5个）</t>
+          <t>接管前夜</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>离岸通道 （，总时长：10秒，镜头数：4个）</t>
+          <t>离岸通道</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>黑账锁死 （，总时长：11秒，镜头数：4个）</t>
+          <t>黑账锁死</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>第三方现声 （，总时长：10秒，镜头数：4个）</t>
+          <t>第三方现声</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>天香楼邀约 （，总时长：12秒，镜头数：4个）</t>
+          <t>天香楼邀约</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>暗处监控 （，总时长：11秒，镜头数：5个）</t>
+          <t>暗处监控</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
